--- a/Valuation_Table.xlsx.xlsx
+++ b/Valuation_Table.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC4E5CD-59D9-4B03-8EB7-93913270A39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7E053E-F453-43C9-984F-B6C9BD42DBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{41C2374E-C430-40AE-8F55-923DD2E59F49}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Company</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Walmart vs. Average</t>
+  </si>
+  <si>
+    <t>Educational Project – Not Financial Advice</t>
   </si>
 </sst>
 </file>
@@ -96,7 +99,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\+0.00;\-0.00;0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +156,23 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -221,7 +241,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -268,6 +288,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -277,20 +355,11 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -341,6 +410,24 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -682,7 +769,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B92A10-210B-4AF6-B2FC-BFAA4A2166A4}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.625" style="1" customWidth="1"/>
@@ -690,153 +777,166 @@
     <col min="3" max="6" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="24"/>
+    </row>
+    <row r="2" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F2" s="21" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="7">
-        <v>39.46</v>
-      </c>
-      <c r="D2" s="8">
-        <v>9.3800000000000008</v>
-      </c>
-      <c r="E2" s="8">
-        <v>1.23</v>
-      </c>
-      <c r="F2" s="8">
-        <v>19.7</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="11">
-        <v>47.39</v>
-      </c>
-      <c r="D3" s="11">
-        <v>12.6</v>
-      </c>
-      <c r="E3" s="11">
-        <v>1.44</v>
-      </c>
-      <c r="F3" s="11">
-        <v>28.37</v>
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4">
+        <v>39.46</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="F3" s="5">
+        <v>19.7</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="14">
-        <v>19.420000000000002</v>
-      </c>
-      <c r="D4" s="14">
-        <v>4</v>
-      </c>
-      <c r="E4" s="14">
-        <v>0.62</v>
-      </c>
-      <c r="F4" s="14">
-        <v>10.09</v>
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="8">
+        <v>47.39</v>
+      </c>
+      <c r="D4" s="8">
+        <v>12.6</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1.44</v>
+      </c>
+      <c r="F4" s="8">
+        <v>28.37</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
+        <v>19.420000000000002</v>
+      </c>
+      <c r="D5" s="11">
+        <v>4</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.62</v>
+      </c>
+      <c r="F5" s="11">
+        <v>10.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C6" s="8">
         <v>33.22</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D6" s="8">
         <v>5.47</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E6" s="8">
         <v>0.25</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F6" s="8">
         <v>9.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17">
-        <f>AVERAGE(C3:C5)</f>
-        <v>33.343333333333334</v>
-      </c>
-      <c r="D6" s="18">
-        <f>AVERAGE(D3:D5)</f>
-        <v>7.3566666666666665</v>
-      </c>
-      <c r="E6" s="18">
-        <f>AVERAGE(E3:E5)</f>
-        <v>0.77</v>
-      </c>
-      <c r="F6" s="18">
-        <f>AVERAGE(F3:F5)</f>
-        <v>16.02</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14">
+        <f>AVERAGE(C4:C6)</f>
+        <v>33.343333333333334</v>
+      </c>
+      <c r="D7" s="15">
+        <f>AVERAGE(D4:D6)</f>
+        <v>7.3566666666666665</v>
+      </c>
+      <c r="E7" s="15">
+        <f>AVERAGE(E4:E6)</f>
+        <v>0.77</v>
+      </c>
+      <c r="F7" s="15">
+        <f>AVERAGE(F4:F6)</f>
+        <v>16.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="21">
-        <f>C2 -C6</f>
+      <c r="C8" s="18">
+        <f>C3 -C7</f>
         <v>6.1166666666666671</v>
       </c>
-      <c r="D7" s="21">
-        <f>D2 -D6</f>
+      <c r="D8" s="18">
+        <f>D3 -D7</f>
         <v>2.0233333333333343</v>
       </c>
-      <c r="E7" s="21">
-        <f>E2 -E6</f>
+      <c r="E8" s="18">
+        <f>E3 -E7</f>
         <v>0.45999999999999996</v>
       </c>
-      <c r="F7" s="21">
-        <f>F2 -F6</f>
+      <c r="F8" s="18">
+        <f>F3 -F7</f>
         <v>3.6799999999999997</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
